--- a/frontend/public/templates/sample_evaluation.xlsx
+++ b/frontend/public/templates/sample_evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YEAR3\TERM-2\CAPSTONE-2\lecturer-contract-management-system\frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE8827C-DB7A-4B63-BE14-0EB59A1411EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7CECA1-3373-4A12-A4BA-04B374493669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -172,6 +172,15 @@
   </si>
   <si>
     <t>Software Engineering Group 4</t>
+  </si>
+  <si>
+    <t>Hello g1</t>
+  </si>
+  <si>
+    <t>hello g2</t>
+  </si>
+  <si>
+    <t>hello hsahfga</t>
   </si>
 </sst>
 </file>
@@ -894,6 +903,9 @@
       <c r="L2">
         <v>3</v>
       </c>
+      <c r="M2" t="s">
+        <v>49</v>
+      </c>
       <c r="N2">
         <v>4</v>
       </c>
@@ -908,6 +920,9 @@
       </c>
       <c r="R2">
         <v>5</v>
+      </c>
+      <c r="S2" t="s">
+        <v>51</v>
       </c>
       <c r="T2">
         <v>4</v>
@@ -1001,6 +1016,9 @@
       </c>
       <c r="L3">
         <v>4</v>
+      </c>
+      <c r="M3" t="s">
+        <v>50</v>
       </c>
       <c r="N3">
         <v>4</v>
